--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -3434,11 +3434,11 @@
         <v>118196060</v>
       </c>
       <c r="B29" t="n">
-        <v>56502</v>
+        <v>56687</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -3434,7 +3434,7 @@
         <v>118196060</v>
       </c>
       <c r="B29" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,7 +4043,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571848</v>
+        <v>124571847</v>
       </c>
       <c r="B35" t="n">
         <v>91919</v>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695979</v>
+        <v>695987</v>
       </c>
       <c r="R35" t="n">
-        <v>7393955</v>
+        <v>7393957</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571853</v>
+        <v>124571845</v>
       </c>
       <c r="B36" t="n">
-        <v>92285</v>
+        <v>91919</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696047</v>
+        <v>695985</v>
       </c>
       <c r="R36" t="n">
-        <v>7394073</v>
+        <v>7393935</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571850</v>
+        <v>124571860</v>
       </c>
       <c r="B37" t="n">
-        <v>92309</v>
+        <v>57662</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>103022</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696053</v>
+        <v>695887</v>
       </c>
       <c r="R37" t="n">
-        <v>7394088</v>
+        <v>7393600</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4349,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571866</v>
+        <v>124571846</v>
       </c>
       <c r="B38" t="n">
-        <v>92287</v>
+        <v>91919</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696053</v>
+        <v>696031</v>
       </c>
       <c r="R38" t="n">
-        <v>7394088</v>
+        <v>7394057</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4433,7 +4433,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4452,7 +4451,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571846</v>
+        <v>124571844</v>
       </c>
       <c r="B39" t="n">
         <v>91919</v>
@@ -4492,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696031</v>
+        <v>695985</v>
       </c>
       <c r="R39" t="n">
-        <v>7394057</v>
+        <v>7393933</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4656,7 +4655,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571844</v>
+        <v>124571848</v>
       </c>
       <c r="B41" t="n">
         <v>91919</v>
@@ -4696,10 +4695,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695985</v>
+        <v>695979</v>
       </c>
       <c r="R41" t="n">
-        <v>7393933</v>
+        <v>7393955</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4758,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571847</v>
+        <v>124571850</v>
       </c>
       <c r="B42" t="n">
-        <v>91919</v>
+        <v>92309</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4774,21 +4773,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4798,10 +4797,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695987</v>
+        <v>696053</v>
       </c>
       <c r="R42" t="n">
-        <v>7393957</v>
+        <v>7394088</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4860,10 +4859,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571843</v>
+        <v>124571866</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>92287</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4876,21 +4875,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4900,10 +4899,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695886</v>
+        <v>696053</v>
       </c>
       <c r="R43" t="n">
-        <v>7393602</v>
+        <v>7394088</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4930,17 +4929,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4949,6 +4943,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4967,10 +4962,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571860</v>
+        <v>124571843</v>
       </c>
       <c r="B44" t="n">
-        <v>57662</v>
+        <v>57666</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4983,21 +4978,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103022</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695887</v>
+        <v>695886</v>
       </c>
       <c r="R44" t="n">
-        <v>7393600</v>
+        <v>7393602</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5043,6 +5038,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571845</v>
+        <v>124571854</v>
       </c>
       <c r="B45" t="n">
-        <v>91919</v>
+        <v>92328</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695985</v>
+        <v>695754</v>
       </c>
       <c r="R45" t="n">
-        <v>7393935</v>
+        <v>7393607</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571854</v>
+        <v>124571853</v>
       </c>
       <c r="B46" t="n">
-        <v>92328</v>
+        <v>92285</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695754</v>
+        <v>696047</v>
       </c>
       <c r="R46" t="n">
-        <v>7393607</v>
+        <v>7394073</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571847</v>
+        <v>124571850</v>
       </c>
       <c r="B35" t="n">
-        <v>91919</v>
+        <v>92309</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695987</v>
+        <v>696053</v>
       </c>
       <c r="R35" t="n">
-        <v>7393957</v>
+        <v>7394088</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571845</v>
+        <v>124571844</v>
       </c>
       <c r="B36" t="n">
         <v>91919</v>
@@ -4188,7 +4188,7 @@
         <v>695985</v>
       </c>
       <c r="R36" t="n">
-        <v>7393935</v>
+        <v>7393933</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571860</v>
+        <v>124571847</v>
       </c>
       <c r="B37" t="n">
-        <v>57662</v>
+        <v>91919</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103022</v>
+        <v>4745</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695887</v>
+        <v>695987</v>
       </c>
       <c r="R37" t="n">
-        <v>7393600</v>
+        <v>7393957</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4349,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571846</v>
+        <v>124571866</v>
       </c>
       <c r="B38" t="n">
-        <v>91919</v>
+        <v>92287</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696031</v>
+        <v>696053</v>
       </c>
       <c r="R38" t="n">
-        <v>7394057</v>
+        <v>7394088</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4433,6 +4433,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4451,7 +4452,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571844</v>
+        <v>124571846</v>
       </c>
       <c r="B39" t="n">
         <v>91919</v>
@@ -4491,10 +4492,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695985</v>
+        <v>696031</v>
       </c>
       <c r="R39" t="n">
-        <v>7393933</v>
+        <v>7394057</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4553,10 +4554,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571849</v>
+        <v>124571843</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4569,21 +4570,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4593,10 +4594,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696056</v>
+        <v>695886</v>
       </c>
       <c r="R40" t="n">
-        <v>7394080</v>
+        <v>7393602</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4623,12 +4624,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4757,10 +4763,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571850</v>
+        <v>124571860</v>
       </c>
       <c r="B42" t="n">
-        <v>92309</v>
+        <v>57662</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4773,21 +4779,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>103022</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4797,10 +4803,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696053</v>
+        <v>695887</v>
       </c>
       <c r="R42" t="n">
-        <v>7394088</v>
+        <v>7393600</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4827,12 +4833,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4859,10 +4865,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571866</v>
+        <v>124571854</v>
       </c>
       <c r="B43" t="n">
-        <v>92287</v>
+        <v>92328</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4875,21 +4881,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4899,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696053</v>
+        <v>695754</v>
       </c>
       <c r="R43" t="n">
-        <v>7394088</v>
+        <v>7393607</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4943,7 +4949,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4962,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571843</v>
+        <v>124571849</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4978,21 +4983,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5002,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695886</v>
+        <v>696056</v>
       </c>
       <c r="R44" t="n">
-        <v>7393602</v>
+        <v>7394080</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5032,17 +5037,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571854</v>
+        <v>124571853</v>
       </c>
       <c r="B45" t="n">
-        <v>92328</v>
+        <v>92285</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695754</v>
+        <v>696047</v>
       </c>
       <c r="R45" t="n">
-        <v>7393607</v>
+        <v>7394073</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571853</v>
+        <v>124571845</v>
       </c>
       <c r="B46" t="n">
-        <v>92285</v>
+        <v>91919</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696047</v>
+        <v>695985</v>
       </c>
       <c r="R46" t="n">
-        <v>7394073</v>
+        <v>7393935</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571850</v>
+        <v>124571844</v>
       </c>
       <c r="B35" t="n">
-        <v>92309</v>
+        <v>91919</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696053</v>
+        <v>695985</v>
       </c>
       <c r="R35" t="n">
-        <v>7394088</v>
+        <v>7393933</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571844</v>
+        <v>124571848</v>
       </c>
       <c r="B36" t="n">
         <v>91919</v>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695985</v>
+        <v>695979</v>
       </c>
       <c r="R36" t="n">
-        <v>7393933</v>
+        <v>7393955</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571847</v>
+        <v>124571853</v>
       </c>
       <c r="B37" t="n">
-        <v>91919</v>
+        <v>92285</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695987</v>
+        <v>696047</v>
       </c>
       <c r="R37" t="n">
-        <v>7393957</v>
+        <v>7394073</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571866</v>
+        <v>124571847</v>
       </c>
       <c r="B38" t="n">
-        <v>92287</v>
+        <v>91919</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696053</v>
+        <v>695987</v>
       </c>
       <c r="R38" t="n">
-        <v>7394088</v>
+        <v>7393957</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4433,7 +4433,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4452,10 +4451,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571846</v>
+        <v>124571860</v>
       </c>
       <c r="B39" t="n">
-        <v>91919</v>
+        <v>57662</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4468,21 +4467,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4745</v>
+        <v>103022</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4492,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696031</v>
+        <v>695887</v>
       </c>
       <c r="R39" t="n">
-        <v>7394057</v>
+        <v>7393600</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4522,12 +4521,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4661,7 +4660,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571848</v>
+        <v>124571845</v>
       </c>
       <c r="B41" t="n">
         <v>91919</v>
@@ -4701,10 +4700,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695979</v>
+        <v>695985</v>
       </c>
       <c r="R41" t="n">
-        <v>7393955</v>
+        <v>7393935</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4763,10 +4762,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571860</v>
+        <v>124571866</v>
       </c>
       <c r="B42" t="n">
-        <v>57662</v>
+        <v>92287</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4779,21 +4778,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103022</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4803,10 +4802,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695887</v>
+        <v>696053</v>
       </c>
       <c r="R42" t="n">
-        <v>7393600</v>
+        <v>7394088</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4833,12 +4832,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4847,6 +4846,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4865,10 +4865,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571854</v>
+        <v>124571846</v>
       </c>
       <c r="B43" t="n">
-        <v>92328</v>
+        <v>91919</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695754</v>
+        <v>696031</v>
       </c>
       <c r="R43" t="n">
-        <v>7393607</v>
+        <v>7394057</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4967,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571849</v>
+        <v>124571854</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>92328</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696056</v>
+        <v>695754</v>
       </c>
       <c r="R44" t="n">
-        <v>7394080</v>
+        <v>7393607</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571853</v>
+        <v>124571849</v>
       </c>
       <c r="B45" t="n">
-        <v>92285</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696047</v>
+        <v>696056</v>
       </c>
       <c r="R45" t="n">
-        <v>7394073</v>
+        <v>7394080</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571845</v>
+        <v>124571850</v>
       </c>
       <c r="B46" t="n">
-        <v>91919</v>
+        <v>92309</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695985</v>
+        <v>696053</v>
       </c>
       <c r="R46" t="n">
-        <v>7393935</v>
+        <v>7394088</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,7 +4043,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571844</v>
+        <v>124571847</v>
       </c>
       <c r="B35" t="n">
         <v>91919</v>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695985</v>
+        <v>695987</v>
       </c>
       <c r="R35" t="n">
-        <v>7393933</v>
+        <v>7393957</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571848</v>
+        <v>124571853</v>
       </c>
       <c r="B36" t="n">
-        <v>91919</v>
+        <v>92285</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695979</v>
+        <v>696047</v>
       </c>
       <c r="R36" t="n">
-        <v>7393955</v>
+        <v>7394073</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571853</v>
+        <v>124571866</v>
       </c>
       <c r="B37" t="n">
-        <v>92285</v>
+        <v>92287</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696047</v>
+        <v>696053</v>
       </c>
       <c r="R37" t="n">
-        <v>7394073</v>
+        <v>7394088</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4331,6 +4331,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4349,7 +4350,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571847</v>
+        <v>124571845</v>
       </c>
       <c r="B38" t="n">
         <v>91919</v>
@@ -4389,10 +4390,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695987</v>
+        <v>695985</v>
       </c>
       <c r="R38" t="n">
-        <v>7393957</v>
+        <v>7393935</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4451,10 +4452,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571860</v>
+        <v>124571846</v>
       </c>
       <c r="B39" t="n">
-        <v>57662</v>
+        <v>91919</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4467,21 +4468,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103022</v>
+        <v>4745</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4492,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695887</v>
+        <v>696031</v>
       </c>
       <c r="R39" t="n">
-        <v>7393600</v>
+        <v>7394057</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4521,12 +4522,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4553,10 +4554,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571843</v>
+        <v>124571854</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>92328</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4569,21 +4570,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4593,10 +4594,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695886</v>
+        <v>695754</v>
       </c>
       <c r="R40" t="n">
-        <v>7393602</v>
+        <v>7393607</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4623,17 +4624,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4660,7 +4656,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571845</v>
+        <v>124571844</v>
       </c>
       <c r="B41" t="n">
         <v>91919</v>
@@ -4703,7 +4699,7 @@
         <v>695985</v>
       </c>
       <c r="R41" t="n">
-        <v>7393935</v>
+        <v>7393933</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4762,10 +4758,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571866</v>
+        <v>124571848</v>
       </c>
       <c r="B42" t="n">
-        <v>92287</v>
+        <v>91919</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4778,21 +4774,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4802,10 +4798,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696053</v>
+        <v>695979</v>
       </c>
       <c r="R42" t="n">
-        <v>7394088</v>
+        <v>7393955</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4846,7 +4842,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4865,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571846</v>
+        <v>124571843</v>
       </c>
       <c r="B43" t="n">
-        <v>91919</v>
+        <v>57666</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4881,21 +4876,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4900,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696031</v>
+        <v>695886</v>
       </c>
       <c r="R43" t="n">
-        <v>7394057</v>
+        <v>7393602</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4935,12 +4930,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4967,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571854</v>
+        <v>124571850</v>
       </c>
       <c r="B44" t="n">
-        <v>92328</v>
+        <v>92309</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695754</v>
+        <v>696053</v>
       </c>
       <c r="R44" t="n">
-        <v>7393607</v>
+        <v>7394088</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571849</v>
+        <v>124571860</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>57662</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>103022</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696056</v>
+        <v>695887</v>
       </c>
       <c r="R45" t="n">
-        <v>7394080</v>
+        <v>7393600</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571850</v>
+        <v>124571849</v>
       </c>
       <c r="B46" t="n">
-        <v>92309</v>
+        <v>57529</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696053</v>
+        <v>696056</v>
       </c>
       <c r="R46" t="n">
-        <v>7394088</v>
+        <v>7394080</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>
@@ -5241,12 +5241,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4758,10 +4758,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571848</v>
+        <v>124571843</v>
       </c>
       <c r="B42" t="n">
-        <v>91919</v>
+        <v>57666</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4774,21 +4774,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695979</v>
+        <v>695886</v>
       </c>
       <c r="R42" t="n">
-        <v>7393955</v>
+        <v>7393602</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4828,12 +4828,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4860,10 +4865,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571843</v>
+        <v>124571848</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>91919</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4876,21 +4881,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>4745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4900,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695886</v>
+        <v>695979</v>
       </c>
       <c r="R43" t="n">
-        <v>7393602</v>
+        <v>7393955</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4930,17 +4935,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,7 +4043,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571847</v>
+        <v>124571846</v>
       </c>
       <c r="B35" t="n">
         <v>91919</v>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695987</v>
+        <v>696031</v>
       </c>
       <c r="R35" t="n">
-        <v>7393957</v>
+        <v>7394057</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571853</v>
+        <v>124571844</v>
       </c>
       <c r="B36" t="n">
-        <v>92285</v>
+        <v>91919</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696047</v>
+        <v>695985</v>
       </c>
       <c r="R36" t="n">
-        <v>7394073</v>
+        <v>7393933</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571866</v>
+        <v>124571848</v>
       </c>
       <c r="B37" t="n">
-        <v>92287</v>
+        <v>91919</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696053</v>
+        <v>695979</v>
       </c>
       <c r="R37" t="n">
-        <v>7394088</v>
+        <v>7393955</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4331,7 +4331,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4350,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571845</v>
+        <v>124571853</v>
       </c>
       <c r="B38" t="n">
-        <v>91919</v>
+        <v>92285</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4366,21 +4365,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4390,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695985</v>
+        <v>696047</v>
       </c>
       <c r="R38" t="n">
-        <v>7393935</v>
+        <v>7394073</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4452,7 +4451,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571846</v>
+        <v>124571845</v>
       </c>
       <c r="B39" t="n">
         <v>91919</v>
@@ -4492,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696031</v>
+        <v>695985</v>
       </c>
       <c r="R39" t="n">
-        <v>7394057</v>
+        <v>7393935</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4554,10 +4553,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571854</v>
+        <v>124571847</v>
       </c>
       <c r="B40" t="n">
-        <v>92328</v>
+        <v>91919</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4570,21 +4569,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4594,10 +4593,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695754</v>
+        <v>695987</v>
       </c>
       <c r="R40" t="n">
-        <v>7393607</v>
+        <v>7393957</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4656,10 +4655,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571844</v>
+        <v>124571843</v>
       </c>
       <c r="B41" t="n">
-        <v>91919</v>
+        <v>57666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4672,21 +4671,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4696,10 +4695,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695985</v>
+        <v>695886</v>
       </c>
       <c r="R41" t="n">
-        <v>7393933</v>
+        <v>7393602</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4726,12 +4725,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4758,10 +4762,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571843</v>
+        <v>124571849</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4774,21 +4778,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4798,10 +4802,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695886</v>
+        <v>696056</v>
       </c>
       <c r="R42" t="n">
-        <v>7393602</v>
+        <v>7394080</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4828,17 +4832,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4865,10 +4864,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571848</v>
+        <v>124571866</v>
       </c>
       <c r="B43" t="n">
-        <v>91919</v>
+        <v>92287</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4881,21 +4880,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4904,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695979</v>
+        <v>696053</v>
       </c>
       <c r="R43" t="n">
-        <v>7393955</v>
+        <v>7394088</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4949,6 +4948,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4967,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571850</v>
+        <v>124571860</v>
       </c>
       <c r="B44" t="n">
-        <v>92309</v>
+        <v>57662</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>103022</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696053</v>
+        <v>695887</v>
       </c>
       <c r="R44" t="n">
-        <v>7394088</v>
+        <v>7393600</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571860</v>
+        <v>124571850</v>
       </c>
       <c r="B45" t="n">
-        <v>57662</v>
+        <v>92309</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103022</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695887</v>
+        <v>696053</v>
       </c>
       <c r="R45" t="n">
-        <v>7393600</v>
+        <v>7394088</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571849</v>
+        <v>124571854</v>
       </c>
       <c r="B46" t="n">
-        <v>57529</v>
+        <v>92328</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696056</v>
+        <v>695754</v>
       </c>
       <c r="R46" t="n">
-        <v>7394080</v>
+        <v>7393607</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>
@@ -5241,12 +5241,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,7 +4043,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571846</v>
+        <v>124571844</v>
       </c>
       <c r="B35" t="n">
         <v>91919</v>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696031</v>
+        <v>695985</v>
       </c>
       <c r="R35" t="n">
-        <v>7394057</v>
+        <v>7393933</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571844</v>
+        <v>124571843</v>
       </c>
       <c r="B36" t="n">
-        <v>91919</v>
+        <v>57666</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695985</v>
+        <v>695886</v>
       </c>
       <c r="R36" t="n">
-        <v>7393933</v>
+        <v>7393602</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4215,12 +4215,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4349,10 +4354,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571853</v>
+        <v>124571847</v>
       </c>
       <c r="B38" t="n">
-        <v>92285</v>
+        <v>91919</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,21 +4370,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696047</v>
+        <v>695987</v>
       </c>
       <c r="R38" t="n">
-        <v>7394073</v>
+        <v>7393957</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4451,10 +4456,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571845</v>
+        <v>124571854</v>
       </c>
       <c r="B39" t="n">
-        <v>91919</v>
+        <v>92328</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4467,21 +4472,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4496,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695985</v>
+        <v>695754</v>
       </c>
       <c r="R39" t="n">
-        <v>7393935</v>
+        <v>7393607</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4553,10 +4558,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571847</v>
+        <v>124571853</v>
       </c>
       <c r="B40" t="n">
-        <v>91919</v>
+        <v>92285</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4569,21 +4574,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4593,10 +4598,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695987</v>
+        <v>696047</v>
       </c>
       <c r="R40" t="n">
-        <v>7393957</v>
+        <v>7394073</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4655,10 +4660,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571843</v>
+        <v>124571849</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4671,21 +4676,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4695,10 +4700,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695886</v>
+        <v>696056</v>
       </c>
       <c r="R41" t="n">
-        <v>7393602</v>
+        <v>7394080</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4725,17 +4730,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4762,10 +4762,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571849</v>
+        <v>124571846</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>91919</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4778,21 +4778,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>4745</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696056</v>
+        <v>696031</v>
       </c>
       <c r="R42" t="n">
-        <v>7394080</v>
+        <v>7394057</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4832,12 +4832,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4864,10 +4864,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571866</v>
+        <v>124571850</v>
       </c>
       <c r="B43" t="n">
-        <v>92287</v>
+        <v>92309</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4880,21 +4880,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4948,7 +4948,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4967,10 +4966,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571860</v>
+        <v>124571866</v>
       </c>
       <c r="B44" t="n">
-        <v>57662</v>
+        <v>92287</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4983,21 +4982,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103022</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,10 +5006,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695887</v>
+        <v>696053</v>
       </c>
       <c r="R44" t="n">
-        <v>7393600</v>
+        <v>7394088</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5037,12 +5036,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5051,6 +5050,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571850</v>
+        <v>124571845</v>
       </c>
       <c r="B45" t="n">
-        <v>92309</v>
+        <v>91919</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696053</v>
+        <v>695985</v>
       </c>
       <c r="R45" t="n">
-        <v>7394088</v>
+        <v>7393935</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571854</v>
+        <v>124571860</v>
       </c>
       <c r="B46" t="n">
-        <v>92328</v>
+        <v>57662</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>103022</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695754</v>
+        <v>695887</v>
       </c>
       <c r="R46" t="n">
-        <v>7393607</v>
+        <v>7393600</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>
@@ -5241,12 +5241,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571844</v>
+        <v>124571866</v>
       </c>
       <c r="B35" t="n">
-        <v>91919</v>
+        <v>92287</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695985</v>
+        <v>696053</v>
       </c>
       <c r="R35" t="n">
-        <v>7393933</v>
+        <v>7394088</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4127,6 +4127,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4145,10 +4146,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571843</v>
+        <v>124571846</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>91919</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4162,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>4745</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695886</v>
+        <v>696031</v>
       </c>
       <c r="R36" t="n">
-        <v>7393602</v>
+        <v>7394057</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4215,17 +4216,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4252,7 +4248,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571848</v>
+        <v>124571845</v>
       </c>
       <c r="B37" t="n">
         <v>91919</v>
@@ -4292,10 +4288,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695979</v>
+        <v>695985</v>
       </c>
       <c r="R37" t="n">
-        <v>7393955</v>
+        <v>7393935</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4354,10 +4350,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571847</v>
+        <v>124571850</v>
       </c>
       <c r="B38" t="n">
-        <v>91919</v>
+        <v>92309</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4370,21 +4366,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4390,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695987</v>
+        <v>696053</v>
       </c>
       <c r="R38" t="n">
-        <v>7393957</v>
+        <v>7394088</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4456,10 +4452,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571854</v>
+        <v>124571843</v>
       </c>
       <c r="B39" t="n">
-        <v>92328</v>
+        <v>57666</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4472,21 +4468,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4496,10 +4492,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695754</v>
+        <v>695886</v>
       </c>
       <c r="R39" t="n">
-        <v>7393607</v>
+        <v>7393602</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4526,12 +4522,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4558,10 +4559,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571853</v>
+        <v>124571847</v>
       </c>
       <c r="B40" t="n">
-        <v>92285</v>
+        <v>91919</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4574,21 +4575,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4598,10 +4599,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696047</v>
+        <v>695987</v>
       </c>
       <c r="R40" t="n">
-        <v>7394073</v>
+        <v>7393957</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4660,10 +4661,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571849</v>
+        <v>124571853</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
+        <v>92285</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4676,21 +4677,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4700,10 +4701,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696056</v>
+        <v>696047</v>
       </c>
       <c r="R41" t="n">
-        <v>7394080</v>
+        <v>7394073</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4730,12 +4731,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4762,7 +4763,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571846</v>
+        <v>124571848</v>
       </c>
       <c r="B42" t="n">
         <v>91919</v>
@@ -4802,10 +4803,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696031</v>
+        <v>695979</v>
       </c>
       <c r="R42" t="n">
-        <v>7394057</v>
+        <v>7393955</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4864,10 +4865,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571850</v>
+        <v>124571854</v>
       </c>
       <c r="B43" t="n">
-        <v>92309</v>
+        <v>92328</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4880,21 +4881,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4904,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696053</v>
+        <v>695754</v>
       </c>
       <c r="R43" t="n">
-        <v>7394088</v>
+        <v>7393607</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4966,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571866</v>
+        <v>124571860</v>
       </c>
       <c r="B44" t="n">
-        <v>92287</v>
+        <v>57662</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4982,21 +4983,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>103022</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5006,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696053</v>
+        <v>695887</v>
       </c>
       <c r="R44" t="n">
-        <v>7394088</v>
+        <v>7393600</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5036,12 +5037,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5050,7 +5051,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571845</v>
+        <v>124571849</v>
       </c>
       <c r="B45" t="n">
-        <v>91919</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4745</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695985</v>
+        <v>696056</v>
       </c>
       <c r="R45" t="n">
-        <v>7393935</v>
+        <v>7394080</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571860</v>
+        <v>124571844</v>
       </c>
       <c r="B46" t="n">
-        <v>57662</v>
+        <v>91919</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103022</v>
+        <v>4745</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695887</v>
+        <v>695985</v>
       </c>
       <c r="R46" t="n">
-        <v>7393600</v>
+        <v>7393933</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>
@@ -5241,12 +5241,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571866</v>
+        <v>124571850</v>
       </c>
       <c r="B35" t="n">
-        <v>92287</v>
+        <v>92309</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4127,7 +4127,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4146,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571846</v>
+        <v>124571860</v>
       </c>
       <c r="B36" t="n">
-        <v>91919</v>
+        <v>57662</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4162,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4745</v>
+        <v>103022</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696031</v>
+        <v>695887</v>
       </c>
       <c r="R36" t="n">
-        <v>7394057</v>
+        <v>7393600</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4216,12 +4215,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4248,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571845</v>
+        <v>124571866</v>
       </c>
       <c r="B37" t="n">
-        <v>91919</v>
+        <v>92287</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4264,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4288,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695985</v>
+        <v>696053</v>
       </c>
       <c r="R37" t="n">
-        <v>7393935</v>
+        <v>7394088</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4332,6 +4331,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571850</v>
+        <v>124571846</v>
       </c>
       <c r="B38" t="n">
-        <v>92309</v>
+        <v>91919</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696053</v>
+        <v>696031</v>
       </c>
       <c r="R38" t="n">
-        <v>7394088</v>
+        <v>7394057</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571843</v>
+        <v>124571849</v>
       </c>
       <c r="B39" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4468,21 +4468,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695886</v>
+        <v>696056</v>
       </c>
       <c r="R39" t="n">
-        <v>7393602</v>
+        <v>7394080</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4522,17 +4522,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4559,10 +4554,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571847</v>
+        <v>124571853</v>
       </c>
       <c r="B40" t="n">
-        <v>91919</v>
+        <v>92285</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4575,21 +4570,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4599,10 +4594,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695987</v>
+        <v>696047</v>
       </c>
       <c r="R40" t="n">
-        <v>7393957</v>
+        <v>7394073</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4661,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571853</v>
+        <v>124571843</v>
       </c>
       <c r="B41" t="n">
-        <v>92285</v>
+        <v>57666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4677,21 +4672,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4701,10 +4696,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696047</v>
+        <v>695886</v>
       </c>
       <c r="R41" t="n">
-        <v>7394073</v>
+        <v>7393602</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4731,12 +4726,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4763,10 +4763,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571848</v>
+        <v>124571854</v>
       </c>
       <c r="B42" t="n">
-        <v>91919</v>
+        <v>92328</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4779,21 +4779,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695979</v>
+        <v>695754</v>
       </c>
       <c r="R42" t="n">
-        <v>7393955</v>
+        <v>7393607</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4865,10 +4865,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571854</v>
+        <v>124571844</v>
       </c>
       <c r="B43" t="n">
-        <v>92328</v>
+        <v>91919</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695754</v>
+        <v>695985</v>
       </c>
       <c r="R43" t="n">
-        <v>7393607</v>
+        <v>7393933</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4967,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571860</v>
+        <v>124571848</v>
       </c>
       <c r="B44" t="n">
-        <v>57662</v>
+        <v>91919</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103022</v>
+        <v>4745</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695887</v>
+        <v>695979</v>
       </c>
       <c r="R44" t="n">
-        <v>7393600</v>
+        <v>7393955</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571849</v>
+        <v>124571847</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>91919</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>4745</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696056</v>
+        <v>695987</v>
       </c>
       <c r="R45" t="n">
-        <v>7394080</v>
+        <v>7393957</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5171,7 +5171,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571844</v>
+        <v>124571845</v>
       </c>
       <c r="B46" t="n">
         <v>91919</v>
@@ -5214,7 +5214,7 @@
         <v>695985</v>
       </c>
       <c r="R46" t="n">
-        <v>7393933</v>
+        <v>7393935</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571843</v>
+        <v>124571854</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>92328</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4672,21 +4672,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695886</v>
+        <v>695754</v>
       </c>
       <c r="R41" t="n">
-        <v>7393602</v>
+        <v>7393607</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4726,17 +4726,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4763,10 +4758,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571854</v>
+        <v>124571843</v>
       </c>
       <c r="B42" t="n">
-        <v>92328</v>
+        <v>57666</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4779,21 +4774,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4803,10 +4798,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695754</v>
+        <v>695886</v>
       </c>
       <c r="R42" t="n">
-        <v>7393607</v>
+        <v>7393602</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4833,12 +4828,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571850</v>
+        <v>124571848</v>
       </c>
       <c r="B35" t="n">
-        <v>92309</v>
+        <v>91919</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696053</v>
+        <v>695979</v>
       </c>
       <c r="R35" t="n">
-        <v>7394088</v>
+        <v>7393955</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571860</v>
+        <v>124571866</v>
       </c>
       <c r="B36" t="n">
-        <v>57662</v>
+        <v>92287</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103022</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695887</v>
+        <v>696053</v>
       </c>
       <c r="R36" t="n">
-        <v>7393600</v>
+        <v>7394088</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4229,6 +4229,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4247,10 +4248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571866</v>
+        <v>124571844</v>
       </c>
       <c r="B37" t="n">
-        <v>92287</v>
+        <v>91919</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4264,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4288,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696053</v>
+        <v>695985</v>
       </c>
       <c r="R37" t="n">
-        <v>7394088</v>
+        <v>7393933</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4331,7 +4332,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571846</v>
+        <v>124571853</v>
       </c>
       <c r="B38" t="n">
-        <v>91919</v>
+        <v>92285</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696031</v>
+        <v>696047</v>
       </c>
       <c r="R38" t="n">
-        <v>7394057</v>
+        <v>7394073</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571849</v>
+        <v>124571845</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>91919</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4468,21 +4468,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>4745</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696056</v>
+        <v>695985</v>
       </c>
       <c r="R39" t="n">
-        <v>7394080</v>
+        <v>7393935</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4522,12 +4522,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4554,10 +4554,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571853</v>
+        <v>124571860</v>
       </c>
       <c r="B40" t="n">
-        <v>92285</v>
+        <v>57662</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>103022</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696047</v>
+        <v>695887</v>
       </c>
       <c r="R40" t="n">
-        <v>7394073</v>
+        <v>7393600</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571854</v>
+        <v>124571849</v>
       </c>
       <c r="B41" t="n">
-        <v>92328</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4672,21 +4672,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695754</v>
+        <v>696056</v>
       </c>
       <c r="R41" t="n">
-        <v>7393607</v>
+        <v>7394080</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571843</v>
+        <v>124571854</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>92328</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4774,21 +4774,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695886</v>
+        <v>695754</v>
       </c>
       <c r="R42" t="n">
-        <v>7393602</v>
+        <v>7393607</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4828,17 +4828,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4865,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571844</v>
+        <v>124571850</v>
       </c>
       <c r="B43" t="n">
-        <v>91919</v>
+        <v>92309</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4881,21 +4876,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4900,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695985</v>
+        <v>696053</v>
       </c>
       <c r="R43" t="n">
-        <v>7393933</v>
+        <v>7394088</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4967,7 +4962,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571848</v>
+        <v>124571846</v>
       </c>
       <c r="B44" t="n">
         <v>91919</v>
@@ -5007,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695979</v>
+        <v>696031</v>
       </c>
       <c r="R44" t="n">
-        <v>7393955</v>
+        <v>7394057</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5171,10 +5166,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571845</v>
+        <v>124571843</v>
       </c>
       <c r="B46" t="n">
-        <v>91919</v>
+        <v>57666</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5182,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5206,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695985</v>
+        <v>695886</v>
       </c>
       <c r="R46" t="n">
-        <v>7393935</v>
+        <v>7393602</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>
@@ -5241,12 +5236,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571848</v>
+        <v>124571866</v>
       </c>
       <c r="B35" t="n">
-        <v>91919</v>
+        <v>92287</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695979</v>
+        <v>696053</v>
       </c>
       <c r="R35" t="n">
-        <v>7393955</v>
+        <v>7394088</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4127,6 +4127,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4145,10 +4146,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571866</v>
+        <v>124571853</v>
       </c>
       <c r="B36" t="n">
-        <v>92287</v>
+        <v>92285</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4162,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696053</v>
+        <v>696047</v>
       </c>
       <c r="R36" t="n">
-        <v>7394088</v>
+        <v>7394073</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4229,7 +4230,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571844</v>
+        <v>124571848</v>
       </c>
       <c r="B37" t="n">
         <v>91919</v>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695985</v>
+        <v>695979</v>
       </c>
       <c r="R37" t="n">
-        <v>7393933</v>
+        <v>7393955</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571853</v>
+        <v>124571845</v>
       </c>
       <c r="B38" t="n">
-        <v>92285</v>
+        <v>91919</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696047</v>
+        <v>695985</v>
       </c>
       <c r="R38" t="n">
-        <v>7394073</v>
+        <v>7393935</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571845</v>
+        <v>124571849</v>
       </c>
       <c r="B39" t="n">
-        <v>91919</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4468,21 +4468,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4745</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695985</v>
+        <v>696056</v>
       </c>
       <c r="R39" t="n">
-        <v>7393935</v>
+        <v>7394080</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4522,12 +4522,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4554,10 +4554,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571860</v>
+        <v>124571844</v>
       </c>
       <c r="B40" t="n">
-        <v>57662</v>
+        <v>91919</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4570,21 +4570,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103022</v>
+        <v>4745</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695887</v>
+        <v>695985</v>
       </c>
       <c r="R40" t="n">
-        <v>7393600</v>
+        <v>7393933</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4656,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571849</v>
+        <v>124571854</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
+        <v>92328</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4672,21 +4672,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696056</v>
+        <v>695754</v>
       </c>
       <c r="R41" t="n">
-        <v>7394080</v>
+        <v>7393607</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571854</v>
+        <v>124571846</v>
       </c>
       <c r="B42" t="n">
-        <v>92328</v>
+        <v>91919</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4774,21 +4774,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695754</v>
+        <v>696031</v>
       </c>
       <c r="R42" t="n">
-        <v>7393607</v>
+        <v>7394057</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571850</v>
+        <v>124571847</v>
       </c>
       <c r="B43" t="n">
-        <v>92309</v>
+        <v>91919</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4876,21 +4876,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4900,10 +4900,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696053</v>
+        <v>695987</v>
       </c>
       <c r="R43" t="n">
-        <v>7394088</v>
+        <v>7393957</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4962,10 +4962,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571846</v>
+        <v>124571843</v>
       </c>
       <c r="B44" t="n">
-        <v>91919</v>
+        <v>57666</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4978,21 +4978,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696031</v>
+        <v>695886</v>
       </c>
       <c r="R44" t="n">
-        <v>7394057</v>
+        <v>7393602</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5032,12 +5032,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5064,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571847</v>
+        <v>124571860</v>
       </c>
       <c r="B45" t="n">
-        <v>91919</v>
+        <v>57662</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5080,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4745</v>
+        <v>103022</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5104,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695987</v>
+        <v>695887</v>
       </c>
       <c r="R45" t="n">
-        <v>7393957</v>
+        <v>7393600</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5134,12 +5139,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5166,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571843</v>
+        <v>124571850</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>92309</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5182,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5206,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695886</v>
+        <v>696053</v>
       </c>
       <c r="R46" t="n">
-        <v>7393602</v>
+        <v>7394088</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>
@@ -5236,17 +5241,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571866</v>
+        <v>124571843</v>
       </c>
       <c r="B35" t="n">
-        <v>92287</v>
+        <v>57666</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696053</v>
+        <v>695886</v>
       </c>
       <c r="R35" t="n">
-        <v>7394088</v>
+        <v>7393602</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4113,12 +4113,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4127,7 +4132,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4146,10 +4150,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571853</v>
+        <v>124571847</v>
       </c>
       <c r="B36" t="n">
-        <v>92285</v>
+        <v>91919</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4162,21 +4166,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4190,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696047</v>
+        <v>695987</v>
       </c>
       <c r="R36" t="n">
-        <v>7394073</v>
+        <v>7393957</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4248,10 +4252,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571848</v>
+        <v>124571860</v>
       </c>
       <c r="B37" t="n">
-        <v>91919</v>
+        <v>57662</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4264,21 +4268,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4745</v>
+        <v>103022</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4288,10 +4292,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695979</v>
+        <v>695887</v>
       </c>
       <c r="R37" t="n">
-        <v>7393955</v>
+        <v>7393600</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4318,12 +4322,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4350,10 +4354,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571845</v>
+        <v>124571850</v>
       </c>
       <c r="B38" t="n">
-        <v>91919</v>
+        <v>92309</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4366,21 +4370,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4390,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695985</v>
+        <v>696053</v>
       </c>
       <c r="R38" t="n">
-        <v>7393935</v>
+        <v>7394088</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4452,10 +4456,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571849</v>
+        <v>124571848</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>91919</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4468,21 +4472,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>4745</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4492,10 +4496,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696056</v>
+        <v>695979</v>
       </c>
       <c r="R39" t="n">
-        <v>7394080</v>
+        <v>7393955</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4522,12 +4526,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4554,7 +4558,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571844</v>
+        <v>124571846</v>
       </c>
       <c r="B40" t="n">
         <v>91919</v>
@@ -4594,10 +4598,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695985</v>
+        <v>696031</v>
       </c>
       <c r="R40" t="n">
-        <v>7393933</v>
+        <v>7394057</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4656,10 +4660,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571854</v>
+        <v>124571866</v>
       </c>
       <c r="B41" t="n">
-        <v>92328</v>
+        <v>92287</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4672,21 +4676,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4696,10 +4700,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695754</v>
+        <v>696053</v>
       </c>
       <c r="R41" t="n">
-        <v>7393607</v>
+        <v>7394088</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4740,6 +4744,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4758,10 +4763,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571846</v>
+        <v>124571854</v>
       </c>
       <c r="B42" t="n">
-        <v>91919</v>
+        <v>92328</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4774,21 +4779,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4798,10 +4803,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696031</v>
+        <v>695754</v>
       </c>
       <c r="R42" t="n">
-        <v>7394057</v>
+        <v>7393607</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4860,10 +4865,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571847</v>
+        <v>124571853</v>
       </c>
       <c r="B43" t="n">
-        <v>91919</v>
+        <v>92285</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4876,21 +4881,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4900,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695987</v>
+        <v>696047</v>
       </c>
       <c r="R43" t="n">
-        <v>7393957</v>
+        <v>7394073</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4962,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571843</v>
+        <v>124571849</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4978,21 +4983,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5002,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695886</v>
+        <v>696056</v>
       </c>
       <c r="R44" t="n">
-        <v>7393602</v>
+        <v>7394080</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5032,17 +5037,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571860</v>
+        <v>124571844</v>
       </c>
       <c r="B45" t="n">
-        <v>57662</v>
+        <v>91919</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103022</v>
+        <v>4745</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695887</v>
+        <v>695985</v>
       </c>
       <c r="R45" t="n">
-        <v>7393600</v>
+        <v>7393933</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571850</v>
+        <v>124571845</v>
       </c>
       <c r="B46" t="n">
-        <v>92309</v>
+        <v>91919</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696053</v>
+        <v>695985</v>
       </c>
       <c r="R46" t="n">
-        <v>7394088</v>
+        <v>7393935</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571843</v>
+        <v>124571854</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>92328</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695886</v>
+        <v>695754</v>
       </c>
       <c r="R35" t="n">
-        <v>7393602</v>
+        <v>7393607</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4113,17 +4113,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4150,7 +4145,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571847</v>
+        <v>124571848</v>
       </c>
       <c r="B36" t="n">
         <v>91919</v>
@@ -4190,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695987</v>
+        <v>695979</v>
       </c>
       <c r="R36" t="n">
-        <v>7393957</v>
+        <v>7393955</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4354,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571850</v>
+        <v>124571843</v>
       </c>
       <c r="B38" t="n">
-        <v>92309</v>
+        <v>57666</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4370,21 +4365,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696053</v>
+        <v>695886</v>
       </c>
       <c r="R38" t="n">
-        <v>7394088</v>
+        <v>7393602</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4424,12 +4419,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4456,10 +4456,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571848</v>
+        <v>124571866</v>
       </c>
       <c r="B39" t="n">
-        <v>91919</v>
+        <v>92287</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4472,21 +4472,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695979</v>
+        <v>696053</v>
       </c>
       <c r="R39" t="n">
-        <v>7393955</v>
+        <v>7394088</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4540,6 +4540,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4660,10 +4661,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571866</v>
+        <v>124571845</v>
       </c>
       <c r="B41" t="n">
-        <v>92287</v>
+        <v>91919</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4676,21 +4677,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4700,10 +4701,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696053</v>
+        <v>695985</v>
       </c>
       <c r="R41" t="n">
-        <v>7394088</v>
+        <v>7393935</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4744,7 +4745,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4763,10 +4763,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571854</v>
+        <v>124571850</v>
       </c>
       <c r="B42" t="n">
-        <v>92328</v>
+        <v>92309</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4779,21 +4779,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695754</v>
+        <v>696053</v>
       </c>
       <c r="R42" t="n">
-        <v>7393607</v>
+        <v>7394088</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4865,10 +4865,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571853</v>
+        <v>124571844</v>
       </c>
       <c r="B43" t="n">
-        <v>92285</v>
+        <v>91919</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696047</v>
+        <v>695985</v>
       </c>
       <c r="R43" t="n">
-        <v>7394073</v>
+        <v>7393933</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571844</v>
+        <v>124571853</v>
       </c>
       <c r="B45" t="n">
-        <v>91919</v>
+        <v>92285</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695985</v>
+        <v>696047</v>
       </c>
       <c r="R45" t="n">
-        <v>7393933</v>
+        <v>7394073</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5171,7 +5171,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571845</v>
+        <v>124571847</v>
       </c>
       <c r="B46" t="n">
         <v>91919</v>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695985</v>
+        <v>695987</v>
       </c>
       <c r="R46" t="n">
-        <v>7393935</v>
+        <v>7393957</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571854</v>
+        <v>124571853</v>
       </c>
       <c r="B35" t="n">
-        <v>92328</v>
+        <v>92285</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695754</v>
+        <v>696047</v>
       </c>
       <c r="R35" t="n">
-        <v>7393607</v>
+        <v>7394073</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571848</v>
+        <v>124571866</v>
       </c>
       <c r="B36" t="n">
-        <v>91919</v>
+        <v>92287</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695979</v>
+        <v>696053</v>
       </c>
       <c r="R36" t="n">
-        <v>7393955</v>
+        <v>7394088</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4229,6 +4229,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4247,10 +4248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571860</v>
+        <v>124571849</v>
       </c>
       <c r="B37" t="n">
-        <v>57662</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4264,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103022</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4288,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695887</v>
+        <v>696056</v>
       </c>
       <c r="R37" t="n">
-        <v>7393600</v>
+        <v>7394080</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4317,12 +4318,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4456,10 +4457,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571866</v>
+        <v>124571846</v>
       </c>
       <c r="B39" t="n">
-        <v>92287</v>
+        <v>91919</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4472,21 +4473,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4496,10 +4497,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696053</v>
+        <v>696031</v>
       </c>
       <c r="R39" t="n">
-        <v>7394088</v>
+        <v>7394057</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4540,7 +4541,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4559,7 +4559,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571846</v>
+        <v>124571844</v>
       </c>
       <c r="B40" t="n">
         <v>91919</v>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696031</v>
+        <v>695985</v>
       </c>
       <c r="R40" t="n">
-        <v>7394057</v>
+        <v>7393933</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571845</v>
+        <v>124571854</v>
       </c>
       <c r="B41" t="n">
-        <v>91919</v>
+        <v>92328</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695985</v>
+        <v>695754</v>
       </c>
       <c r="R41" t="n">
-        <v>7393935</v>
+        <v>7393607</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571844</v>
+        <v>124571845</v>
       </c>
       <c r="B43" t="n">
         <v>91919</v>
@@ -4908,7 +4908,7 @@
         <v>695985</v>
       </c>
       <c r="R43" t="n">
-        <v>7393933</v>
+        <v>7393935</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4967,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571849</v>
+        <v>124571847</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>91919</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>4745</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696056</v>
+        <v>695987</v>
       </c>
       <c r="R44" t="n">
-        <v>7394080</v>
+        <v>7393957</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571853</v>
+        <v>124571848</v>
       </c>
       <c r="B45" t="n">
-        <v>92285</v>
+        <v>91919</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696047</v>
+        <v>695979</v>
       </c>
       <c r="R45" t="n">
-        <v>7394073</v>
+        <v>7393955</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571847</v>
+        <v>124571860</v>
       </c>
       <c r="B46" t="n">
-        <v>91919</v>
+        <v>57662</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4745</v>
+        <v>103022</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695987</v>
+        <v>695887</v>
       </c>
       <c r="R46" t="n">
-        <v>7393957</v>
+        <v>7393600</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>
@@ -5241,12 +5241,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571853</v>
+        <v>124571844</v>
       </c>
       <c r="B35" t="n">
-        <v>92285</v>
+        <v>91919</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696047</v>
+        <v>695985</v>
       </c>
       <c r="R35" t="n">
-        <v>7394073</v>
+        <v>7393933</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571866</v>
+        <v>124571854</v>
       </c>
       <c r="B36" t="n">
-        <v>92287</v>
+        <v>92328</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696053</v>
+        <v>695754</v>
       </c>
       <c r="R36" t="n">
-        <v>7394088</v>
+        <v>7393607</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4229,7 +4229,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4248,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571849</v>
+        <v>124571845</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>91919</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4264,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>4745</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4288,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696056</v>
+        <v>695985</v>
       </c>
       <c r="R37" t="n">
-        <v>7394080</v>
+        <v>7393935</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4318,12 +4317,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4350,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571843</v>
+        <v>124571850</v>
       </c>
       <c r="B38" t="n">
-        <v>57666</v>
+        <v>92309</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4366,21 +4365,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4390,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695886</v>
+        <v>696053</v>
       </c>
       <c r="R38" t="n">
-        <v>7393602</v>
+        <v>7394088</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4420,17 +4419,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4457,10 +4451,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571846</v>
+        <v>124571860</v>
       </c>
       <c r="B39" t="n">
-        <v>91919</v>
+        <v>57662</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4473,21 +4467,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4745</v>
+        <v>103022</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4497,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696031</v>
+        <v>695887</v>
       </c>
       <c r="R39" t="n">
-        <v>7394057</v>
+        <v>7393600</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4527,12 +4521,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4559,7 +4553,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571844</v>
+        <v>124571847</v>
       </c>
       <c r="B40" t="n">
         <v>91919</v>
@@ -4599,10 +4593,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695985</v>
+        <v>695987</v>
       </c>
       <c r="R40" t="n">
-        <v>7393933</v>
+        <v>7393957</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4661,10 +4655,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571854</v>
+        <v>124571853</v>
       </c>
       <c r="B41" t="n">
-        <v>92328</v>
+        <v>92285</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4677,21 +4671,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4701,10 +4695,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695754</v>
+        <v>696047</v>
       </c>
       <c r="R41" t="n">
-        <v>7393607</v>
+        <v>7394073</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4763,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571850</v>
+        <v>124571849</v>
       </c>
       <c r="B42" t="n">
-        <v>92309</v>
+        <v>57529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4779,21 +4773,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4803,10 +4797,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696053</v>
+        <v>696056</v>
       </c>
       <c r="R42" t="n">
-        <v>7394088</v>
+        <v>7394080</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4833,12 +4827,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4865,7 +4859,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571845</v>
+        <v>124571846</v>
       </c>
       <c r="B43" t="n">
         <v>91919</v>
@@ -4905,10 +4899,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695985</v>
+        <v>696031</v>
       </c>
       <c r="R43" t="n">
-        <v>7393935</v>
+        <v>7394057</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4967,10 +4961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571847</v>
+        <v>124571843</v>
       </c>
       <c r="B44" t="n">
-        <v>91919</v>
+        <v>57666</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4983,21 +4977,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,10 +5001,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695987</v>
+        <v>695886</v>
       </c>
       <c r="R44" t="n">
-        <v>7393957</v>
+        <v>7393602</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5037,12 +5031,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5171,10 +5170,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571860</v>
+        <v>124571866</v>
       </c>
       <c r="B46" t="n">
-        <v>57662</v>
+        <v>92287</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5186,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103022</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5210,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695887</v>
+        <v>696053</v>
       </c>
       <c r="R46" t="n">
-        <v>7393600</v>
+        <v>7394088</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>
@@ -5241,12 +5240,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5255,6 +5254,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571844</v>
+        <v>124571854</v>
       </c>
       <c r="B35" t="n">
-        <v>91919</v>
+        <v>92328</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4745</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695985</v>
+        <v>695754</v>
       </c>
       <c r="R35" t="n">
-        <v>7393933</v>
+        <v>7393607</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571854</v>
+        <v>124571847</v>
       </c>
       <c r="B36" t="n">
-        <v>92328</v>
+        <v>91919</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695754</v>
+        <v>695987</v>
       </c>
       <c r="R36" t="n">
-        <v>7393607</v>
+        <v>7393957</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571845</v>
+        <v>124571850</v>
       </c>
       <c r="B37" t="n">
-        <v>91919</v>
+        <v>92309</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695985</v>
+        <v>696053</v>
       </c>
       <c r="R37" t="n">
-        <v>7393935</v>
+        <v>7394088</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571850</v>
+        <v>124571860</v>
       </c>
       <c r="B38" t="n">
-        <v>92309</v>
+        <v>57662</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>103022</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696053</v>
+        <v>695887</v>
       </c>
       <c r="R38" t="n">
-        <v>7394088</v>
+        <v>7393600</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4419,12 +4419,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4451,10 +4451,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571860</v>
+        <v>124571866</v>
       </c>
       <c r="B39" t="n">
-        <v>57662</v>
+        <v>92287</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103022</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>695887</v>
+        <v>696053</v>
       </c>
       <c r="R39" t="n">
-        <v>7393600</v>
+        <v>7394088</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -4521,12 +4521,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4535,6 +4535,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4553,10 +4554,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571847</v>
+        <v>124571843</v>
       </c>
       <c r="B40" t="n">
-        <v>91919</v>
+        <v>57666</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4569,21 +4570,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4745</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4593,10 +4594,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695987</v>
+        <v>695886</v>
       </c>
       <c r="R40" t="n">
-        <v>7393957</v>
+        <v>7393602</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4623,12 +4624,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4757,10 +4763,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571849</v>
+        <v>124571848</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>91919</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4773,21 +4779,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>4745</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4797,10 +4803,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696056</v>
+        <v>695979</v>
       </c>
       <c r="R42" t="n">
-        <v>7394080</v>
+        <v>7393955</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4827,12 +4833,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4859,7 +4865,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571846</v>
+        <v>124571845</v>
       </c>
       <c r="B43" t="n">
         <v>91919</v>
@@ -4899,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696031</v>
+        <v>695985</v>
       </c>
       <c r="R43" t="n">
-        <v>7394057</v>
+        <v>7393935</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4961,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571843</v>
+        <v>124571846</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>91919</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4977,21 +4983,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>4745</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5001,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>695886</v>
+        <v>696031</v>
       </c>
       <c r="R44" t="n">
-        <v>7393602</v>
+        <v>7394057</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5031,17 +5037,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5068,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571848</v>
+        <v>124571849</v>
       </c>
       <c r="B45" t="n">
-        <v>91919</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5084,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4745</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5108,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695979</v>
+        <v>696056</v>
       </c>
       <c r="R45" t="n">
-        <v>7393955</v>
+        <v>7394080</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5138,12 +5139,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5170,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571866</v>
+        <v>124571844</v>
       </c>
       <c r="B46" t="n">
-        <v>92287</v>
+        <v>91919</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5186,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5210,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696053</v>
+        <v>695985</v>
       </c>
       <c r="R46" t="n">
-        <v>7394088</v>
+        <v>7393933</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>
@@ -5254,7 +5255,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571854</v>
+        <v>124571843</v>
       </c>
       <c r="B35" t="n">
-        <v>92328</v>
+        <v>57666</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695754</v>
+        <v>695886</v>
       </c>
       <c r="R35" t="n">
-        <v>7393607</v>
+        <v>7393602</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -4113,12 +4113,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4145,10 +4150,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571847</v>
+        <v>124571853</v>
       </c>
       <c r="B36" t="n">
-        <v>91919</v>
+        <v>92285</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4166,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4190,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>695987</v>
+        <v>696047</v>
       </c>
       <c r="R36" t="n">
-        <v>7393957</v>
+        <v>7394073</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -4247,10 +4252,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571850</v>
+        <v>124571845</v>
       </c>
       <c r="B37" t="n">
-        <v>92309</v>
+        <v>91919</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4268,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4292,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696053</v>
+        <v>695985</v>
       </c>
       <c r="R37" t="n">
-        <v>7394088</v>
+        <v>7393935</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
@@ -4349,10 +4354,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571860</v>
+        <v>124571846</v>
       </c>
       <c r="B38" t="n">
-        <v>57662</v>
+        <v>91919</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,21 +4370,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103022</v>
+        <v>4745</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4394,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>695887</v>
+        <v>696031</v>
       </c>
       <c r="R38" t="n">
-        <v>7393600</v>
+        <v>7394057</v>
       </c>
       <c r="S38" t="n">
         <v>2</v>
@@ -4419,12 +4424,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4554,10 +4559,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571843</v>
+        <v>124571860</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>57662</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4570,21 +4575,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>103022</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4594,10 +4599,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695886</v>
+        <v>695887</v>
       </c>
       <c r="R40" t="n">
-        <v>7393602</v>
+        <v>7393600</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4630,11 +4635,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Par</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4661,10 +4661,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571853</v>
+        <v>124571854</v>
       </c>
       <c r="B41" t="n">
-        <v>92285</v>
+        <v>92328</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696047</v>
+        <v>695754</v>
       </c>
       <c r="R41" t="n">
-        <v>7394073</v>
+        <v>7393607</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4763,7 +4763,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571848</v>
+        <v>124571844</v>
       </c>
       <c r="B42" t="n">
         <v>91919</v>
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695979</v>
+        <v>695985</v>
       </c>
       <c r="R42" t="n">
-        <v>7393955</v>
+        <v>7393933</v>
       </c>
       <c r="S42" t="n">
         <v>2</v>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571845</v>
+        <v>124571847</v>
       </c>
       <c r="B43" t="n">
         <v>91919</v>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695985</v>
+        <v>695987</v>
       </c>
       <c r="R43" t="n">
-        <v>7393935</v>
+        <v>7393957</v>
       </c>
       <c r="S43" t="n">
         <v>2</v>
@@ -4967,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571846</v>
+        <v>124571849</v>
       </c>
       <c r="B44" t="n">
-        <v>91919</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4745</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696031</v>
+        <v>696056</v>
       </c>
       <c r="R44" t="n">
-        <v>7394057</v>
+        <v>7394080</v>
       </c>
       <c r="S44" t="n">
         <v>2</v>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571849</v>
+        <v>124571848</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>91919</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>4745</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696056</v>
+        <v>695979</v>
       </c>
       <c r="R45" t="n">
-        <v>7394080</v>
+        <v>7393955</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5139,12 +5139,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5171,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571844</v>
+        <v>124571850</v>
       </c>
       <c r="B46" t="n">
-        <v>91919</v>
+        <v>92309</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5187,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695985</v>
+        <v>696053</v>
       </c>
       <c r="R46" t="n">
-        <v>7393933</v>
+        <v>7394088</v>
       </c>
       <c r="S46" t="n">
         <v>2</v>

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113337626</v>
+        <v>113337642</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>639</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696041</v>
+        <v>696010</v>
       </c>
       <c r="R2" t="n">
-        <v>7394011</v>
+        <v>7393881</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113337630</v>
+        <v>118196083</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>695883</v>
+        <v>695885</v>
       </c>
       <c r="R3" t="n">
-        <v>7393724</v>
+        <v>7393710</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113337635</v>
+        <v>118196085</v>
       </c>
       <c r="B4" t="n">
-        <v>79016</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229830</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>695828</v>
+        <v>695895</v>
       </c>
       <c r="R4" t="n">
-        <v>7393666</v>
+        <v>7393642</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113337634</v>
+        <v>118196086</v>
       </c>
       <c r="B5" t="n">
-        <v>79016</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229830</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>695912</v>
+        <v>695857</v>
       </c>
       <c r="R5" t="n">
-        <v>7393785</v>
+        <v>7393594</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113337619</v>
+        <v>118196087</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>695961</v>
+        <v>695750</v>
       </c>
       <c r="R6" t="n">
-        <v>7393857</v>
+        <v>7393594</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1153,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113337642</v>
+        <v>124571850</v>
       </c>
       <c r="B7" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>639</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696010</v>
+        <v>696053</v>
       </c>
       <c r="R7" t="n">
-        <v>7393881</v>
+        <v>7394088</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113337625</v>
+        <v>113337637</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696047</v>
+        <v>696014</v>
       </c>
       <c r="R8" t="n">
-        <v>7394021</v>
+        <v>7393879</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113337622</v>
+        <v>118196075</v>
       </c>
       <c r="B9" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696064</v>
+        <v>695883</v>
       </c>
       <c r="R9" t="n">
-        <v>7394083</v>
+        <v>7393708</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1459,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113337629</v>
+        <v>124571853</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696015</v>
+        <v>696047</v>
       </c>
       <c r="R10" t="n">
-        <v>7393874</v>
+        <v>7394073</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113337637</v>
+        <v>124571866</v>
       </c>
       <c r="B11" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696014</v>
+        <v>696053</v>
       </c>
       <c r="R11" t="n">
-        <v>7393879</v>
+        <v>7394088</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,6 +1627,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1695,15 +1646,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113337624</v>
+        <v>124571844</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1657,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4745</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1681,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696053</v>
+        <v>695985</v>
       </c>
       <c r="R12" t="n">
-        <v>7394058</v>
+        <v>7393933</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1765,12 +1711,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,15 +1743,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113337631</v>
+        <v>124571845</v>
       </c>
       <c r="B13" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1754,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>4745</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1778,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>695784</v>
+        <v>695985</v>
       </c>
       <c r="R13" t="n">
-        <v>7393585</v>
+        <v>7393935</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1867,12 +1808,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,15 +1840,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113337623</v>
+        <v>124571846</v>
       </c>
       <c r="B14" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1851,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,13 +1875,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696068</v>
+        <v>696031</v>
       </c>
       <c r="R14" t="n">
-        <v>7394084</v>
+        <v>7394057</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1969,12 +1905,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,15 +1937,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113337636</v>
+        <v>124571847</v>
       </c>
       <c r="B15" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1948,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +1972,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696055</v>
+        <v>695987</v>
       </c>
       <c r="R15" t="n">
-        <v>7394070</v>
+        <v>7393957</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2071,12 +2002,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,15 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113337620</v>
+        <v>124571848</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2045,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,13 +2069,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>695960</v>
+        <v>695979</v>
       </c>
       <c r="R16" t="n">
-        <v>7393866</v>
+        <v>7393955</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2173,12 +2099,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,37 +2131,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118196062</v>
+        <v>124571854</v>
       </c>
       <c r="B17" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,13 +2166,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>695888</v>
+        <v>695754</v>
       </c>
       <c r="R17" t="n">
-        <v>7393714</v>
+        <v>7393607</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2275,12 +2196,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,37 +2228,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118196063</v>
+        <v>118196094</v>
       </c>
       <c r="B18" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>695858</v>
+        <v>695894</v>
       </c>
       <c r="R18" t="n">
-        <v>7393600</v>
+        <v>7393721</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,15 +2325,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118196065</v>
+        <v>118196062</v>
       </c>
       <c r="B19" t="n">
-        <v>79009</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,21 +2336,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229830</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>695982</v>
+        <v>695888</v>
       </c>
       <c r="R19" t="n">
-        <v>7393876</v>
+        <v>7393714</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2493,7 +2404,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2512,37 +2422,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118196046</v>
+        <v>118196063</v>
       </c>
       <c r="B20" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,7 +2457,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>695876</v>
+        <v>695858</v>
       </c>
       <c r="R20" t="n">
         <v>7393600</v>
@@ -2614,37 +2519,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118196083</v>
+        <v>118196098</v>
       </c>
       <c r="B21" t="n">
-        <v>78566</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2654,10 +2554,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695885</v>
+        <v>695858</v>
       </c>
       <c r="R21" t="n">
-        <v>7393710</v>
+        <v>7393599</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2716,32 +2616,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118196091</v>
+        <v>113337636</v>
       </c>
       <c r="B22" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2756,10 +2651,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>695916</v>
+        <v>696055</v>
       </c>
       <c r="R22" t="n">
-        <v>7393662</v>
+        <v>7394070</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2786,12 +2681,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2818,19 +2713,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118196073</v>
+        <v>118196072</v>
       </c>
       <c r="B23" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2858,10 +2748,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696078</v>
+        <v>696018</v>
       </c>
       <c r="R23" t="n">
-        <v>7394109</v>
+        <v>7393988</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2920,15 +2810,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118196068</v>
+        <v>118196073</v>
       </c>
       <c r="B24" t="n">
-        <v>79009</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,21 +2821,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229830</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2845,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>695857</v>
+        <v>696078</v>
       </c>
       <c r="R24" t="n">
-        <v>7393593</v>
+        <v>7394109</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3022,15 +2907,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118196098</v>
+        <v>124571849</v>
       </c>
       <c r="B25" t="n">
-        <v>79600</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,21 +2918,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3062,13 +2942,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>695858</v>
+        <v>696056</v>
       </c>
       <c r="R25" t="n">
-        <v>7393599</v>
+        <v>7394080</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3092,12 +2972,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3124,15 +3004,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118196072</v>
+        <v>113337619</v>
       </c>
       <c r="B26" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3140,16 +3015,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3164,10 +3039,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696018</v>
+        <v>695961</v>
       </c>
       <c r="R26" t="n">
-        <v>7393988</v>
+        <v>7393857</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3194,12 +3069,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3226,37 +3101,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118196066</v>
+        <v>113337620</v>
       </c>
       <c r="B27" t="n">
-        <v>79009</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229830</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3266,10 +3136,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695893</v>
+        <v>695960</v>
       </c>
       <c r="R27" t="n">
-        <v>7393740</v>
+        <v>7393866</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3296,12 +3166,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3310,7 +3180,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3329,15 +3198,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118196085</v>
+        <v>113337622</v>
       </c>
       <c r="B28" t="n">
-        <v>78566</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3345,21 +3209,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3233,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>695895</v>
+        <v>696064</v>
       </c>
       <c r="R28" t="n">
-        <v>7393642</v>
+        <v>7394083</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3399,12 +3263,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3431,37 +3295,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118196060</v>
+        <v>113337623</v>
       </c>
       <c r="B29" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3471,10 +3330,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696058</v>
+        <v>696068</v>
       </c>
       <c r="R29" t="n">
-        <v>7394073</v>
+        <v>7394084</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3501,12 +3360,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3533,37 +3392,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118196069</v>
+        <v>113337624</v>
       </c>
       <c r="B30" t="n">
-        <v>79009</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229830</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3573,10 +3427,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>695780</v>
+        <v>696053</v>
       </c>
       <c r="R30" t="n">
-        <v>7393616</v>
+        <v>7394058</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3603,12 +3457,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3635,15 +3489,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118196075</v>
+        <v>113337625</v>
       </c>
       <c r="B31" t="n">
-        <v>79566</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3651,21 +3500,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3524,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>695883</v>
+        <v>696047</v>
       </c>
       <c r="R31" t="n">
-        <v>7393708</v>
+        <v>7394021</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3705,12 +3554,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3737,15 +3586,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118196094</v>
+        <v>113337626</v>
       </c>
       <c r="B32" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3753,21 +3597,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3777,10 +3621,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>695894</v>
+        <v>696041</v>
       </c>
       <c r="R32" t="n">
-        <v>7393721</v>
+        <v>7394011</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3807,12 +3651,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3839,15 +3683,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118196090</v>
+        <v>113337629</v>
       </c>
       <c r="B33" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3855,16 +3694,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3879,10 +3718,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696074</v>
+        <v>696015</v>
       </c>
       <c r="R33" t="n">
-        <v>7394037</v>
+        <v>7393874</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3909,12 +3748,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3941,15 +3780,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118196086</v>
+        <v>113337630</v>
       </c>
       <c r="B34" t="n">
-        <v>78566</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3957,21 +3791,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3981,10 +3815,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>695857</v>
+        <v>695883</v>
       </c>
       <c r="R34" t="n">
-        <v>7393594</v>
+        <v>7393724</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4011,12 +3845,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4043,15 +3877,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124571843</v>
+        <v>118196046</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4059,21 +3888,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,13 +3912,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>695886</v>
+        <v>695876</v>
       </c>
       <c r="R35" t="n">
-        <v>7393602</v>
+        <v>7393600</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4113,17 +3942,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4150,37 +3974,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124571853</v>
+        <v>118196060</v>
       </c>
       <c r="B36" t="n">
-        <v>92285</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4190,13 +4009,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696047</v>
+        <v>696058</v>
       </c>
       <c r="R36" t="n">
         <v>7394073</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4220,12 +4039,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4252,37 +4071,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124571845</v>
+        <v>118196090</v>
       </c>
       <c r="B37" t="n">
-        <v>91919</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4745</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4292,13 +4106,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>695985</v>
+        <v>696074</v>
       </c>
       <c r="R37" t="n">
-        <v>7393935</v>
+        <v>7394037</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4322,12 +4136,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4354,37 +4168,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124571846</v>
+        <v>118196091</v>
       </c>
       <c r="B38" t="n">
-        <v>91919</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4745</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,13 +4203,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696031</v>
+        <v>695916</v>
       </c>
       <c r="R38" t="n">
-        <v>7394057</v>
+        <v>7393662</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4424,12 +4233,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4456,15 +4265,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124571866</v>
+        <v>113337631</v>
       </c>
       <c r="B39" t="n">
-        <v>92287</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4472,21 +4276,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4496,13 +4300,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696053</v>
+        <v>695784</v>
       </c>
       <c r="R39" t="n">
-        <v>7394088</v>
+        <v>7393585</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4526,12 +4330,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4540,7 +4344,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4559,15 +4362,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124571860</v>
+        <v>124571843</v>
       </c>
       <c r="B40" t="n">
-        <v>57662</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4575,21 +4373,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103022</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4599,10 +4397,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695887</v>
+        <v>695886</v>
       </c>
       <c r="R40" t="n">
-        <v>7393600</v>
+        <v>7393602</v>
       </c>
       <c r="S40" t="n">
         <v>2</v>
@@ -4635,6 +4433,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4661,15 +4464,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124571854</v>
+        <v>124571860</v>
       </c>
       <c r="B41" t="n">
-        <v>92328</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4677,21 +4475,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>103022</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4701,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695754</v>
+        <v>695887</v>
       </c>
       <c r="R41" t="n">
-        <v>7393607</v>
+        <v>7393600</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4731,12 +4529,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4763,37 +4561,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124571844</v>
+        <v>113337634</v>
       </c>
       <c r="B42" t="n">
-        <v>91919</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79853</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4745</v>
+        <v>229830</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Späd brosklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Ramalina dilacerata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4803,13 +4596,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695985</v>
+        <v>695912</v>
       </c>
       <c r="R42" t="n">
-        <v>7393933</v>
+        <v>7393785</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4833,12 +4626,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4865,37 +4658,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124571847</v>
+        <v>113337635</v>
       </c>
       <c r="B43" t="n">
-        <v>91919</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79853</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4745</v>
+        <v>229830</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Späd brosklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Ramalina dilacerata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,13 +4693,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695987</v>
+        <v>695828</v>
       </c>
       <c r="R43" t="n">
-        <v>7393957</v>
+        <v>7393666</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4935,12 +4723,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4967,37 +4755,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124571849</v>
+        <v>118196065</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79853</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>229830</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Späd brosklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramalina dilacerata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,13 +4790,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696056</v>
+        <v>695982</v>
       </c>
       <c r="R44" t="n">
-        <v>7394080</v>
+        <v>7393876</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5037,12 +4820,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5051,6 +4834,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5069,37 +4853,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124571848</v>
+        <v>118196066</v>
       </c>
       <c r="B45" t="n">
-        <v>91919</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79853</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4745</v>
+        <v>229830</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Späd brosklav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Ramalina dilacerata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5109,13 +4888,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695979</v>
+        <v>695893</v>
       </c>
       <c r="R45" t="n">
-        <v>7393955</v>
+        <v>7393740</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5139,12 +4918,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5153,6 +4932,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5171,37 +4951,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124571850</v>
+        <v>118196068</v>
       </c>
       <c r="B46" t="n">
-        <v>92309</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79853</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>229830</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Späd brosklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramalina dilacerata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,13 +4986,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696053</v>
+        <v>695857</v>
       </c>
       <c r="R46" t="n">
-        <v>7394088</v>
+        <v>7393593</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5241,12 +5016,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5270,6 +5045,103 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118196069</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79853</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229830</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Späd brosklav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ramalina dilacerata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Pärlälven, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>695780</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7393616</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55330-2023 artfynd.xlsx
+++ b/artfynd/A 55330-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337642</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196083</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196085</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196086</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196087</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571850</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337637</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196075</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571853</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571866</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571844</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571845</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571846</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571847</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571848</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2225,6 +2305,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571854</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2322,6 +2407,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196094</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2419,6 +2509,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196062</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2516,6 +2611,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196063</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2613,6 +2713,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196098</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2710,6 +2815,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337636</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2807,6 +2917,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196072</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2904,6 +3019,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196073</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3001,6 +3121,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571849</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3098,6 +3223,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337619</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3195,6 +3325,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337620</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3292,6 +3427,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337622</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3389,6 +3529,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337623</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3486,6 +3631,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337624</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3583,6 +3733,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337625</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3680,6 +3835,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337626</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3777,6 +3937,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337629</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3874,6 +4039,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337630</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3971,6 +4141,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196046</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4068,6 +4243,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196060</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4165,6 +4345,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196090</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4262,6 +4447,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196091</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4359,6 +4549,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337631</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4461,6 +4656,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571843</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4558,6 +4758,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124571860</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4655,6 +4860,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337634</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4752,6 +4962,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337635</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4850,6 +5065,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196065</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4948,6 +5168,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196066</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5045,6 +5270,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196068</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5142,8 +5372,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118196069</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>